--- a/artfynd/A 59583-2025 artfynd.xlsx
+++ b/artfynd/A 59583-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137327427</v>
       </c>
       <c r="B2" t="n">
-        <v>78529</v>
+        <v>78532</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137327445</v>
       </c>
       <c r="B3" t="n">
-        <v>78529</v>
+        <v>78532</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137327495</v>
       </c>
       <c r="B4" t="n">
-        <v>80489</v>
+        <v>80492</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>137327463</v>
       </c>
       <c r="B5" t="n">
-        <v>79592</v>
+        <v>79595</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137327474</v>
       </c>
       <c r="B6" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>137327494</v>
       </c>
       <c r="B7" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>137327425</v>
       </c>
       <c r="B8" t="n">
-        <v>92173</v>
+        <v>92176</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>137327444</v>
       </c>
       <c r="B9" t="n">
-        <v>92173</v>
+        <v>92176</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>137327458</v>
       </c>
       <c r="B10" t="n">
-        <v>83381</v>
+        <v>83384</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>137327492</v>
       </c>
       <c r="B11" t="n">
-        <v>83381</v>
+        <v>83384</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>137327500</v>
       </c>
       <c r="B12" t="n">
-        <v>83381</v>
+        <v>83384</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>137327438</v>
       </c>
       <c r="B13" t="n">
-        <v>83509</v>
+        <v>83512</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>137327488</v>
       </c>
       <c r="B14" t="n">
-        <v>83509</v>
+        <v>83512</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>137327503</v>
       </c>
       <c r="B15" t="n">
-        <v>83509</v>
+        <v>83512</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>137327471</v>
       </c>
       <c r="B16" t="n">
-        <v>80629</v>
+        <v>80632</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>137327426</v>
       </c>
       <c r="B17" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>137327428</v>
       </c>
       <c r="B18" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>137327441</v>
       </c>
       <c r="B19" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>137327466</v>
       </c>
       <c r="B20" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>137327429</v>
       </c>
       <c r="B21" t="n">
-        <v>83504</v>
+        <v>83507</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>137327434</v>
       </c>
       <c r="B22" t="n">
-        <v>83504</v>
+        <v>83507</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>137327457</v>
       </c>
       <c r="B23" t="n">
-        <v>83504</v>
+        <v>83507</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>137327472</v>
       </c>
       <c r="B24" t="n">
-        <v>80522</v>
+        <v>80525</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         <v>137327451</v>
       </c>
       <c r="B25" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>137327430</v>
       </c>
       <c r="B26" t="n">
-        <v>80633</v>
+        <v>80636</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>137327442</v>
       </c>
       <c r="B27" t="n">
-        <v>80640</v>
+        <v>80643</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>137327456</v>
       </c>
       <c r="B28" t="n">
-        <v>57871</v>
+        <v>57872</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         <v>137327452</v>
       </c>
       <c r="B29" t="n">
-        <v>78518</v>
+        <v>78521</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>137327459</v>
       </c>
       <c r="B30" t="n">
-        <v>78518</v>
+        <v>78521</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 59583-2025 artfynd.xlsx
+++ b/artfynd/A 59583-2025 artfynd.xlsx
@@ -1111,7 +1111,7 @@
         <v>137327474</v>
       </c>
       <c r="B6" t="n">
-        <v>92158</v>
+        <v>92160</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>137327494</v>
       </c>
       <c r="B7" t="n">
-        <v>92158</v>
+        <v>92160</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>137327425</v>
       </c>
       <c r="B8" t="n">
-        <v>92176</v>
+        <v>92178</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>137327444</v>
       </c>
       <c r="B9" t="n">
-        <v>92176</v>
+        <v>92178</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 59583-2025 artfynd.xlsx
+++ b/artfynd/A 59583-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137327427</v>
       </c>
       <c r="B2" t="n">
-        <v>78532</v>
+        <v>78537</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137327445</v>
       </c>
       <c r="B3" t="n">
-        <v>78532</v>
+        <v>78537</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137327495</v>
       </c>
       <c r="B4" t="n">
-        <v>80492</v>
+        <v>80497</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>137327463</v>
       </c>
       <c r="B5" t="n">
-        <v>79595</v>
+        <v>79600</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137327474</v>
       </c>
       <c r="B6" t="n">
-        <v>92160</v>
+        <v>92165</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>137327494</v>
       </c>
       <c r="B7" t="n">
-        <v>92160</v>
+        <v>92165</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>137327425</v>
       </c>
       <c r="B8" t="n">
-        <v>92178</v>
+        <v>92183</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>137327444</v>
       </c>
       <c r="B9" t="n">
-        <v>92178</v>
+        <v>92183</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>137327458</v>
       </c>
       <c r="B10" t="n">
-        <v>83384</v>
+        <v>83389</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>137327492</v>
       </c>
       <c r="B11" t="n">
-        <v>83384</v>
+        <v>83389</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>137327500</v>
       </c>
       <c r="B12" t="n">
-        <v>83384</v>
+        <v>83389</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>137327438</v>
       </c>
       <c r="B13" t="n">
-        <v>83512</v>
+        <v>83517</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>137327488</v>
       </c>
       <c r="B14" t="n">
-        <v>83512</v>
+        <v>83517</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>137327503</v>
       </c>
       <c r="B15" t="n">
-        <v>83512</v>
+        <v>83517</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>137327471</v>
       </c>
       <c r="B16" t="n">
-        <v>80632</v>
+        <v>80637</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>137327426</v>
       </c>
       <c r="B17" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>137327428</v>
       </c>
       <c r="B18" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>137327441</v>
       </c>
       <c r="B19" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>137327466</v>
       </c>
       <c r="B20" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>137327429</v>
       </c>
       <c r="B21" t="n">
-        <v>83507</v>
+        <v>83512</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>137327434</v>
       </c>
       <c r="B22" t="n">
-        <v>83507</v>
+        <v>83512</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>137327457</v>
       </c>
       <c r="B23" t="n">
-        <v>83507</v>
+        <v>83512</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>137327472</v>
       </c>
       <c r="B24" t="n">
-        <v>80525</v>
+        <v>80530</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         <v>137327451</v>
       </c>
       <c r="B25" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>137327430</v>
       </c>
       <c r="B26" t="n">
-        <v>80636</v>
+        <v>80641</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>137327442</v>
       </c>
       <c r="B27" t="n">
-        <v>80643</v>
+        <v>80648</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>137327456</v>
       </c>
       <c r="B28" t="n">
-        <v>57872</v>
+        <v>57873</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         <v>137327452</v>
       </c>
       <c r="B29" t="n">
-        <v>78521</v>
+        <v>78526</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>137327459</v>
       </c>
       <c r="B30" t="n">
-        <v>78521</v>
+        <v>78526</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 59583-2025 artfynd.xlsx
+++ b/artfynd/A 59583-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137327427</v>
       </c>
       <c r="B2" t="n">
-        <v>78537</v>
+        <v>78548</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137327445</v>
       </c>
       <c r="B3" t="n">
-        <v>78537</v>
+        <v>78548</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137327495</v>
       </c>
       <c r="B4" t="n">
-        <v>80497</v>
+        <v>80508</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>137327463</v>
       </c>
       <c r="B5" t="n">
-        <v>79600</v>
+        <v>79611</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137327474</v>
       </c>
       <c r="B6" t="n">
-        <v>92165</v>
+        <v>92177</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>137327494</v>
       </c>
       <c r="B7" t="n">
-        <v>92165</v>
+        <v>92177</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>137327425</v>
       </c>
       <c r="B8" t="n">
-        <v>92183</v>
+        <v>92195</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>137327444</v>
       </c>
       <c r="B9" t="n">
-        <v>92183</v>
+        <v>92195</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>137327458</v>
       </c>
       <c r="B10" t="n">
-        <v>83389</v>
+        <v>83400</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>137327492</v>
       </c>
       <c r="B11" t="n">
-        <v>83389</v>
+        <v>83400</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>137327500</v>
       </c>
       <c r="B12" t="n">
-        <v>83389</v>
+        <v>83400</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>137327438</v>
       </c>
       <c r="B13" t="n">
-        <v>83517</v>
+        <v>83528</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>137327488</v>
       </c>
       <c r="B14" t="n">
-        <v>83517</v>
+        <v>83528</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>137327503</v>
       </c>
       <c r="B15" t="n">
-        <v>83517</v>
+        <v>83528</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>137327471</v>
       </c>
       <c r="B16" t="n">
-        <v>80637</v>
+        <v>80648</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>137327426</v>
       </c>
       <c r="B17" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>137327428</v>
       </c>
       <c r="B18" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>137327441</v>
       </c>
       <c r="B19" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>137327466</v>
       </c>
       <c r="B20" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>137327429</v>
       </c>
       <c r="B21" t="n">
-        <v>83512</v>
+        <v>83523</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>137327434</v>
       </c>
       <c r="B22" t="n">
-        <v>83512</v>
+        <v>83523</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>137327457</v>
       </c>
       <c r="B23" t="n">
-        <v>83512</v>
+        <v>83523</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>137327472</v>
       </c>
       <c r="B24" t="n">
-        <v>80530</v>
+        <v>80541</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         <v>137327451</v>
       </c>
       <c r="B25" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>137327430</v>
       </c>
       <c r="B26" t="n">
-        <v>80641</v>
+        <v>80652</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>137327442</v>
       </c>
       <c r="B27" t="n">
-        <v>80648</v>
+        <v>80659</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         <v>137327452</v>
       </c>
       <c r="B29" t="n">
-        <v>78526</v>
+        <v>78537</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>137327459</v>
       </c>
       <c r="B30" t="n">
-        <v>78526</v>
+        <v>78537</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 59583-2025 artfynd.xlsx
+++ b/artfynd/A 59583-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137327427</v>
       </c>
       <c r="B2" t="n">
-        <v>78548</v>
+        <v>78549</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137327445</v>
       </c>
       <c r="B3" t="n">
-        <v>78548</v>
+        <v>78549</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137327495</v>
       </c>
       <c r="B4" t="n">
-        <v>80508</v>
+        <v>80509</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>137327463</v>
       </c>
       <c r="B5" t="n">
-        <v>79611</v>
+        <v>79612</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137327474</v>
       </c>
       <c r="B6" t="n">
-        <v>92177</v>
+        <v>92178</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>137327494</v>
       </c>
       <c r="B7" t="n">
-        <v>92177</v>
+        <v>92178</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>137327425</v>
       </c>
       <c r="B8" t="n">
-        <v>92195</v>
+        <v>92196</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>137327444</v>
       </c>
       <c r="B9" t="n">
-        <v>92195</v>
+        <v>92196</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>137327458</v>
       </c>
       <c r="B10" t="n">
-        <v>83400</v>
+        <v>83401</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>137327492</v>
       </c>
       <c r="B11" t="n">
-        <v>83400</v>
+        <v>83401</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>137327500</v>
       </c>
       <c r="B12" t="n">
-        <v>83400</v>
+        <v>83401</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>137327438</v>
       </c>
       <c r="B13" t="n">
-        <v>83528</v>
+        <v>83529</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>137327488</v>
       </c>
       <c r="B14" t="n">
-        <v>83528</v>
+        <v>83529</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>137327503</v>
       </c>
       <c r="B15" t="n">
-        <v>83528</v>
+        <v>83529</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>137327471</v>
       </c>
       <c r="B16" t="n">
-        <v>80648</v>
+        <v>80649</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>137327426</v>
       </c>
       <c r="B17" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>137327428</v>
       </c>
       <c r="B18" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>137327441</v>
       </c>
       <c r="B19" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>137327466</v>
       </c>
       <c r="B20" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>137327429</v>
       </c>
       <c r="B21" t="n">
-        <v>83523</v>
+        <v>83524</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>137327434</v>
       </c>
       <c r="B22" t="n">
-        <v>83523</v>
+        <v>83524</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>137327457</v>
       </c>
       <c r="B23" t="n">
-        <v>83523</v>
+        <v>83524</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>137327472</v>
       </c>
       <c r="B24" t="n">
-        <v>80541</v>
+        <v>80542</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         <v>137327451</v>
       </c>
       <c r="B25" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>137327430</v>
       </c>
       <c r="B26" t="n">
-        <v>80652</v>
+        <v>80653</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>137327442</v>
       </c>
       <c r="B27" t="n">
-        <v>80659</v>
+        <v>80660</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         <v>137327452</v>
       </c>
       <c r="B29" t="n">
-        <v>78537</v>
+        <v>78538</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>137327459</v>
       </c>
       <c r="B30" t="n">
-        <v>78537</v>
+        <v>78538</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 59583-2025 artfynd.xlsx
+++ b/artfynd/A 59583-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137327427</v>
       </c>
       <c r="B2" t="n">
-        <v>78549</v>
+        <v>78551</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137327445</v>
       </c>
       <c r="B3" t="n">
-        <v>78549</v>
+        <v>78551</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137327495</v>
       </c>
       <c r="B4" t="n">
-        <v>80509</v>
+        <v>80511</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>137327463</v>
       </c>
       <c r="B5" t="n">
-        <v>79612</v>
+        <v>79614</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137327474</v>
       </c>
       <c r="B6" t="n">
-        <v>92178</v>
+        <v>92181</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>137327494</v>
       </c>
       <c r="B7" t="n">
-        <v>92178</v>
+        <v>92181</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>137327425</v>
       </c>
       <c r="B8" t="n">
-        <v>92196</v>
+        <v>92199</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>137327444</v>
       </c>
       <c r="B9" t="n">
-        <v>92196</v>
+        <v>92199</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>137327458</v>
       </c>
       <c r="B10" t="n">
-        <v>83401</v>
+        <v>83403</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>137327492</v>
       </c>
       <c r="B11" t="n">
-        <v>83401</v>
+        <v>83403</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>137327500</v>
       </c>
       <c r="B12" t="n">
-        <v>83401</v>
+        <v>83403</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>137327438</v>
       </c>
       <c r="B13" t="n">
-        <v>83529</v>
+        <v>83531</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>137327488</v>
       </c>
       <c r="B14" t="n">
-        <v>83529</v>
+        <v>83531</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>137327503</v>
       </c>
       <c r="B15" t="n">
-        <v>83529</v>
+        <v>83531</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>137327471</v>
       </c>
       <c r="B16" t="n">
-        <v>80649</v>
+        <v>80651</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>137327426</v>
       </c>
       <c r="B17" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>137327428</v>
       </c>
       <c r="B18" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>137327441</v>
       </c>
       <c r="B19" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>137327466</v>
       </c>
       <c r="B20" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>137327429</v>
       </c>
       <c r="B21" t="n">
-        <v>83524</v>
+        <v>83526</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>137327434</v>
       </c>
       <c r="B22" t="n">
-        <v>83524</v>
+        <v>83526</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>137327457</v>
       </c>
       <c r="B23" t="n">
-        <v>83524</v>
+        <v>83526</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>137327472</v>
       </c>
       <c r="B24" t="n">
-        <v>80542</v>
+        <v>80544</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         <v>137327451</v>
       </c>
       <c r="B25" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>137327430</v>
       </c>
       <c r="B26" t="n">
-        <v>80653</v>
+        <v>80655</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>137327442</v>
       </c>
       <c r="B27" t="n">
-        <v>80660</v>
+        <v>80662</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         <v>137327452</v>
       </c>
       <c r="B29" t="n">
-        <v>78538</v>
+        <v>78540</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>137327459</v>
       </c>
       <c r="B30" t="n">
-        <v>78538</v>
+        <v>78540</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 59583-2025 artfynd.xlsx
+++ b/artfynd/A 59583-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137327427</v>
       </c>
       <c r="B2" t="n">
-        <v>78551</v>
+        <v>78555</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137327445</v>
       </c>
       <c r="B3" t="n">
-        <v>78551</v>
+        <v>78555</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137327495</v>
       </c>
       <c r="B4" t="n">
-        <v>80511</v>
+        <v>80515</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>137327463</v>
       </c>
       <c r="B5" t="n">
-        <v>79614</v>
+        <v>79618</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137327474</v>
       </c>
       <c r="B6" t="n">
-        <v>92181</v>
+        <v>92185</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>137327494</v>
       </c>
       <c r="B7" t="n">
-        <v>92181</v>
+        <v>92185</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>137327425</v>
       </c>
       <c r="B8" t="n">
-        <v>92199</v>
+        <v>92203</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>137327444</v>
       </c>
       <c r="B9" t="n">
-        <v>92199</v>
+        <v>92203</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>137327458</v>
       </c>
       <c r="B10" t="n">
-        <v>83403</v>
+        <v>83407</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>137327492</v>
       </c>
       <c r="B11" t="n">
-        <v>83403</v>
+        <v>83407</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>137327500</v>
       </c>
       <c r="B12" t="n">
-        <v>83403</v>
+        <v>83407</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>137327438</v>
       </c>
       <c r="B13" t="n">
-        <v>83531</v>
+        <v>83535</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>137327488</v>
       </c>
       <c r="B14" t="n">
-        <v>83531</v>
+        <v>83535</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>137327503</v>
       </c>
       <c r="B15" t="n">
-        <v>83531</v>
+        <v>83535</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>137327471</v>
       </c>
       <c r="B16" t="n">
-        <v>80651</v>
+        <v>80655</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>137327426</v>
       </c>
       <c r="B17" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>137327428</v>
       </c>
       <c r="B18" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>137327441</v>
       </c>
       <c r="B19" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>137327466</v>
       </c>
       <c r="B20" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>137327429</v>
       </c>
       <c r="B21" t="n">
-        <v>83526</v>
+        <v>83530</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>137327434</v>
       </c>
       <c r="B22" t="n">
-        <v>83526</v>
+        <v>83530</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>137327457</v>
       </c>
       <c r="B23" t="n">
-        <v>83526</v>
+        <v>83530</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>137327472</v>
       </c>
       <c r="B24" t="n">
-        <v>80544</v>
+        <v>80548</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         <v>137327451</v>
       </c>
       <c r="B25" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>137327430</v>
       </c>
       <c r="B26" t="n">
-        <v>80655</v>
+        <v>80659</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>137327442</v>
       </c>
       <c r="B27" t="n">
-        <v>80662</v>
+        <v>80666</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>137327456</v>
       </c>
       <c r="B28" t="n">
-        <v>57873</v>
+        <v>57876</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         <v>137327452</v>
       </c>
       <c r="B29" t="n">
-        <v>78540</v>
+        <v>78544</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>137327459</v>
       </c>
       <c r="B30" t="n">
-        <v>78540</v>
+        <v>78544</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
